--- a/PC_2009/AS_030.xlsx
+++ b/PC_2009/AS_030.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,8 +45,14 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -59,8 +65,26 @@
         <bgColor rgb="001F497D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -82,11 +106,53 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="medium">
+        <color rgb="001B365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="double">
+        <color rgb="001B365D"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -102,6 +168,21 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -468,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U249"/>
+  <dimension ref="A1:U251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -511,6 +592,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -16921,81 +17003,235 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="6" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C249" s="7">
+      <c r="A249" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL EVM VOTES</t>
+        </is>
+      </c>
+      <c r="B249" s="9" t="inlineStr"/>
+      <c r="C249" s="10">
         <f>SUM(C6:C248)</f>
         <v/>
       </c>
-      <c r="D249" s="7">
+      <c r="D249" s="10">
         <f>SUM(D6:D248)</f>
         <v/>
       </c>
-      <c r="E249" s="7">
+      <c r="E249" s="10">
         <f>SUM(E6:E248)</f>
         <v/>
       </c>
-      <c r="F249" s="7">
+      <c r="F249" s="10">
         <f>SUM(F6:F248)</f>
         <v/>
       </c>
-      <c r="G249" s="7">
+      <c r="G249" s="10">
         <f>SUM(G6:G248)</f>
         <v/>
       </c>
-      <c r="H249" s="7">
+      <c r="H249" s="10">
         <f>SUM(H6:H248)</f>
         <v/>
       </c>
-      <c r="I249" s="7">
+      <c r="I249" s="10">
         <f>SUM(I6:I248)</f>
         <v/>
       </c>
-      <c r="J249" s="7">
+      <c r="J249" s="10">
         <f>SUM(J6:J248)</f>
         <v/>
       </c>
-      <c r="K249" s="7">
+      <c r="K249" s="10">
         <f>SUM(K6:K248)</f>
         <v/>
       </c>
-      <c r="L249" s="7">
+      <c r="L249" s="10">
         <f>SUM(L6:L248)</f>
         <v/>
       </c>
-      <c r="M249" s="7">
+      <c r="M249" s="10">
         <f>SUM(M6:M248)</f>
         <v/>
       </c>
-      <c r="N249" s="7">
+      <c r="N249" s="10">
         <f>SUM(N6:N248)</f>
         <v/>
       </c>
-      <c r="O249" s="7">
+      <c r="O249" s="10">
         <f>SUM(O6:O248)</f>
         <v/>
       </c>
-      <c r="P249" s="7">
+      <c r="P249" s="10">
         <f>SUM(P6:P248)</f>
         <v/>
       </c>
-      <c r="Q249" s="7">
+      <c r="Q249" s="10">
         <f>SUM(Q6:Q248)</f>
         <v/>
       </c>
-      <c r="R249" s="7">
+      <c r="R249" s="10">
         <f>SUM(R6:R248)</f>
         <v/>
       </c>
-      <c r="S249" s="7">
+      <c r="S249" s="10">
         <f>SUM(S6:S248)</f>
         <v/>
       </c>
-      <c r="T249" s="7">
+      <c r="T249" s="10">
         <f>SUM(T6:T248)</f>
+        <v/>
+      </c>
+      <c r="U249" s="10">
+        <f>SUM(U6:U248)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="11" t="inlineStr">
+        <is>
+          <t>POSTAL BALLOT VOTES</t>
+        </is>
+      </c>
+      <c r="B250" s="12" t="inlineStr"/>
+      <c r="C250" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D250" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E250" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F250" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G250" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H250" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I250" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J250" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K250" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L250" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M250" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N250" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O250" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P250" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q250" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R250" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S250" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T250" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U250" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="14" t="inlineStr">
+        <is>
+          <t>TOTAL VOTES POLLED</t>
+        </is>
+      </c>
+      <c r="B251" s="15" t="inlineStr"/>
+      <c r="C251" s="16">
+        <f>C249+C250</f>
+        <v/>
+      </c>
+      <c r="D251" s="16">
+        <f>D249+D250</f>
+        <v/>
+      </c>
+      <c r="E251" s="16">
+        <f>E249+E250</f>
+        <v/>
+      </c>
+      <c r="F251" s="16">
+        <f>F249+F250</f>
+        <v/>
+      </c>
+      <c r="G251" s="16">
+        <f>G249+G250</f>
+        <v/>
+      </c>
+      <c r="H251" s="16">
+        <f>H249+H250</f>
+        <v/>
+      </c>
+      <c r="I251" s="16">
+        <f>I249+I250</f>
+        <v/>
+      </c>
+      <c r="J251" s="16">
+        <f>J249+J250</f>
+        <v/>
+      </c>
+      <c r="K251" s="16">
+        <f>K249+K250</f>
+        <v/>
+      </c>
+      <c r="L251" s="16">
+        <f>L249+L250</f>
+        <v/>
+      </c>
+      <c r="M251" s="16">
+        <f>M249+M250</f>
+        <v/>
+      </c>
+      <c r="N251" s="16">
+        <f>N249+N250</f>
+        <v/>
+      </c>
+      <c r="O251" s="16">
+        <f>O249+O250</f>
+        <v/>
+      </c>
+      <c r="P251" s="16">
+        <f>P249+P250</f>
+        <v/>
+      </c>
+      <c r="Q251" s="16">
+        <f>Q249+Q250</f>
+        <v/>
+      </c>
+      <c r="R251" s="16">
+        <f>R249+R250</f>
+        <v/>
+      </c>
+      <c r="S251" s="16">
+        <f>S249+S250</f>
+        <v/>
+      </c>
+      <c r="T251" s="16">
+        <f>T249+T250</f>
+        <v/>
+      </c>
+      <c r="U251" s="16">
+        <f>U249+U250</f>
         <v/>
       </c>
     </row>
